--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99585234-2629-4787-9FD4-D1D99B72176C}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A3B287-4E80-4B01-A4AB-89D9DF1D34C0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
     <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Phiếu Đánh Giá Tuần 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -786,4 +787,159 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBDF5B8-2AA8-412F-AEA2-45DED3901939}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A3B287-4E80-4B01-A4AB-89D9DF1D34C0}"/>
+  <xr:revisionPtr revIDLastSave="487" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CBF3F6-B4B0-4A39-8217-DFAECC016CCD}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
     <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="2" r:id="rId2"/>
     <sheet name="Phiếu Đánh Giá Tuần 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Phiếu Đánh Giá Tuần 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -942,4 +943,161 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A820622-7EE8-41F4-8F6D-1D6A96DF6423}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4">
+        <v>5</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0D01F0-2123-4358-8BCD-35AA8360B72F}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B90BEBF-68E9-4BDD-8391-03E5867976AE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="2" r:id="rId2"/>
     <sheet name="Phiếu Đánh Giá Tuần 3" sheetId="3" r:id="rId3"/>
     <sheet name="Phiếu Đánh Giá Tuần 4" sheetId="4" r:id="rId4"/>
-    <sheet name="Phiếu Đánh Giá Tuần 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Phiếu Đánh Giá Tuần 5" sheetId="6" r:id="rId5"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -79,19 +80,97 @@
   </si>
   <si>
     <t>Tiêu chí 04: Ai là người bạn cảm thấy cần nỗ lực và chủ động hơn nữa để đóng góp cho dự án</t>
+  </si>
+  <si>
+    <t>Tên sheet</t>
+  </si>
+  <si>
+    <t>Tháng xếp hạng</t>
+  </si>
+  <si>
+    <t>Thứ tự kỳ</t>
+  </si>
+  <si>
+    <t>Tính vào BXH</t>
+  </si>
+  <si>
+    <t>HƯỚNG DẪN</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Pre-work&amp;Tuần 1</t>
+  </si>
+  <si>
+    <t>07/2026</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mỗi sheet đánh giá cần có đúng một dòng trong bảng cấu hình.</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Nhập tháng theo dạng MM/YYYY, ví dụ 08/2026.</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Thứ tự kỳ dùng để sắp xếp tuần trên trang web.</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Chọn "Không" nếu muốn giữ sheet nhưng không tính vào bảng xếp hạng.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="12"/>
@@ -99,15 +178,8 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,11 +189,20 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF2F75B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -157,11 +238,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -177,12 +280,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -194,8 +312,20 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D5">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Thứ tự kỳ"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tính vào BXH"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -237,72 +367,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -310,55 +382,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -367,13 +399,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -407,24 +439,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -450,7 +471,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -479,9 +500,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
@@ -525,7 +543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -556,7 +574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -589,7 +607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -608,7 +626,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -630,17 +648,12 @@
       <c r="K5" s="6"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448980E8-86AA-41A7-8183-196DA736F1AD}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
@@ -684,7 +697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -717,7 +730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -748,7 +761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -765,7 +778,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -785,17 +798,12 @@
       <c r="K5" s="4"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBDF5B8-2AA8-412F-AEA2-45DED3901939}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
@@ -839,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -872,7 +880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -903,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -918,7 +926,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -940,17 +948,12 @@
       <c r="K5" s="4"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A820622-7EE8-41F4-8F6D-1D6A96DF6423}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
@@ -994,7 +997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,7 +1030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1058,7 +1061,7 @@
       </c>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1077,7 +1080,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -1097,17 +1100,12 @@
       <c r="K5" s="4"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584F0946-2E4E-4C29-86CB-F9609A18CC78}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFB998A-A8B4-4752-97FE-94C1AFC97FBA}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1151,107 +1149,234 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4">
-        <v>4</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11">
+        <v>2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>2</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11">
+        <v>4</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11">
         <v>6</v>
       </c>
-      <c r="D3" s="4">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4">
-        <v>3</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4">
-        <v>3</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11">
+        <v>3</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4"/>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"Có,Không"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B90BEBF-68E9-4BDD-8391-03E5867976AE}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E742538-0B43-4C01-83B0-D84DA4FFD5CE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Chọn "Không" nếu muốn giữ sheet nhưng không tính vào bảng xếp hạng.</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 5</t>
   </si>
 </sst>
 </file>
@@ -264,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -295,6 +298,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -313,7 +319,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D6">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -1254,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1265,7 +1271,7 @@
     <col min="7" max="7" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
@@ -1284,7 +1290,7 @@
       </c>
       <c r="G1" s="9"/>
     </row>
-    <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
@@ -1305,7 +1311,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
         <v>25</v>
       </c>
@@ -1326,7 +1332,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
         <v>28</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>31</v>
       </c>
@@ -1366,6 +1372,20 @@
       </c>
       <c r="G5" s="8" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12">
+        <v>46235</v>
+      </c>
+      <c r="C6" s="10">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E742538-0B43-4C01-83B0-D84DA4FFD5CE}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51033F5B-AE83-4645-8C7E-A84EB62D1481}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 3" sheetId="3" r:id="rId3"/>
     <sheet name="Phiếu Đánh Giá Tuần 4" sheetId="4" r:id="rId4"/>
     <sheet name="Phiếu Đánh Giá Tuần 5" sheetId="6" r:id="rId5"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId6"/>
+    <sheet name="Phiếu Đánh Giá Tuần 6" sheetId="7" r:id="rId6"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="36">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -140,13 +141,16 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 5</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +184,10 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -319,7 +327,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D7">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -1259,8 +1267,152 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408660B-958B-414E-9321-65C28591C3FA}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11">
+        <v>2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>1</v>
+      </c>
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11">
+        <v>4</v>
+      </c>
+      <c r="I2" s="11">
+        <v>4</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>2</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>4</v>
+      </c>
+      <c r="E3" s="11">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1379,7 +1531,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="12">
-        <v>46235</v>
+        <v>46966</v>
       </c>
       <c r="C6" s="10">
         <v>5</v>
@@ -1388,9 +1540,24 @@
         <v>22</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46966</v>
+      </c>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="D2:D201" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Tập đoàn/Web đánh giá Dự án/mới/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51033F5B-AE83-4645-8C7E-A84EB62D1481}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029F0E6D-945D-4934-A855-4624E8C11497}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 4" sheetId="4" r:id="rId4"/>
     <sheet name="Phiếu Đánh Giá Tuần 5" sheetId="6" r:id="rId5"/>
     <sheet name="Phiếu Đánh Giá Tuần 6" sheetId="7" r:id="rId6"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId7"/>
+    <sheet name="Phiếu Đánh Giá Tuần 7" sheetId="8" r:id="rId7"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="37">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -144,6 +145,9 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 6</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 7</t>
   </si>
 </sst>
 </file>
@@ -327,7 +331,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D8">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -1411,8 +1415,152 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE812F39-65C1-4566-8CDF-BFF408EB0953}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11">
+        <v>3</v>
+      </c>
+      <c r="K2" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>5</v>
+      </c>
+      <c r="C3" s="11">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11">
+        <v>2</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2</v>
+      </c>
+      <c r="G3" s="11">
+        <v>2</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11">
+        <v>2</v>
+      </c>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1554,10 +1702,24 @@
         <v>22</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46966</v>
+      </c>
+      <c r="C8" s="10">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D201" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="D2:D202" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029F0E6D-945D-4934-A855-4624E8C11497}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F712D20-C0F6-4F6C-B65C-BD8FDABD947C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,16 @@
     <sheet name="Phiếu Đánh Giá Tuần 5" sheetId="6" r:id="rId5"/>
     <sheet name="Phiếu Đánh Giá Tuần 6" sheetId="7" r:id="rId6"/>
     <sheet name="Phiếu Đánh Giá Tuần 7" sheetId="8" r:id="rId7"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId8"/>
+    <sheet name="Phiếu Đánh Giá Tuần 8" sheetId="10" r:id="rId8"/>
+    <sheet name="Phiếu Đánh Giá Tuần 9" sheetId="9" r:id="rId9"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="39">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -148,6 +150,12 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 7</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 8</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 9</t>
   </si>
 </sst>
 </file>
@@ -331,7 +339,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D10">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -670,6 +678,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12">
+        <v>46966</v>
+      </c>
+      <c r="C6" s="10">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46966</v>
+      </c>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46966</v>
+      </c>
+      <c r="C8" s="10">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46235</v>
+      </c>
+      <c r="C9" s="10">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C10" s="10">
+        <v>9</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="D2:D204" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"Có,Không"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K5"/>
@@ -1559,173 +1767,305 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907FA075-1BD6-4B8C-86BB-4F7050351A74}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="10">
-        <v>2</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="10">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="10">
-        <v>4</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="12">
-        <v>46966</v>
-      </c>
-      <c r="C6" s="10">
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="12">
-        <v>46966</v>
-      </c>
-      <c r="C7" s="10">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="12">
-        <v>46966</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>4</v>
+      </c>
+      <c r="J2" s="11">
+        <v>2</v>
+      </c>
+      <c r="K2" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11">
+        <v>3</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D202" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Có,Không"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08850CEF-6A39-4C58-A5BB-0C3D9FDA6609}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>4</v>
+      </c>
+      <c r="J2" s="11">
+        <v>2</v>
+      </c>
+      <c r="K2" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>1</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11">
+        <v>3</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F712D20-C0F6-4F6C-B65C-BD8FDABD947C}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7030EF6-5118-4427-AE6C-A5E81740A11B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -319,7 +319,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="12">
-        <v>46966</v>
+        <v>46235</v>
       </c>
       <c r="C6" s="10">
         <v>5</v>
@@ -813,7 +813,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="12">
-        <v>46966</v>
+        <v>46235</v>
       </c>
       <c r="C7" s="10">
         <v>6</v>
@@ -827,7 +827,7 @@
         <v>36</v>
       </c>
       <c r="B8" s="12">
-        <v>46966</v>
+        <v>46235</v>
       </c>
       <c r="C8" s="10">
         <v>7</v>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7030EF6-5118-4427-AE6C-A5E81740A11B}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F515D827-8D03-4F94-BA64-DA1651CEB3B9}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -22,14 +22,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 7" sheetId="8" r:id="rId7"/>
     <sheet name="Phiếu Đánh Giá Tuần 8" sheetId="10" r:id="rId8"/>
     <sheet name="Phiếu Đánh Giá Tuần 9" sheetId="9" r:id="rId9"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId10"/>
+    <sheet name="Phiếu Đánh Giá Tuần 10" sheetId="11" r:id="rId10"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="40">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -156,6 +157,9 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 9</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 10</t>
   </si>
 </sst>
 </file>
@@ -339,7 +343,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D11">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -679,8 +683,150 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BD8984-E71D-4437-B1FA-142A427C2104}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11">
+        <v>3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>2</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>4</v>
+      </c>
+      <c r="E3" s="11">
+        <v>7</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11">
+        <v>2</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -864,10 +1010,24 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C11" s="10">
+        <v>10</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D204" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="D2:D205" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F515D827-8D03-4F94-BA64-DA1651CEB3B9}"/>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029977AD-504C-4154-8EA1-9011E1C78E37}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -23,14 +23,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 8" sheetId="10" r:id="rId8"/>
     <sheet name="Phiếu Đánh Giá Tuần 9" sheetId="9" r:id="rId9"/>
     <sheet name="Phiếu Đánh Giá Tuần 10" sheetId="11" r:id="rId10"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId11"/>
+    <sheet name="Phiếu Đánh Giá Tuần 11" sheetId="12" r:id="rId11"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="41">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -160,6 +161,9 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 10</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 11</t>
   </si>
 </sst>
 </file>
@@ -343,7 +347,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D12">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -825,8 +829,156 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7600F0A6-54FC-4659-B0E4-F95250E37F83}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>4</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
+        <v>2</v>
+      </c>
+      <c r="I3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1024,10 +1176,24 @@
         <v>22</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="12">
+        <v>46296</v>
+      </c>
+      <c r="C12" s="10">
+        <v>11</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D205" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="D2:D206" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/mới/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="314" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029977AD-504C-4154-8EA1-9011E1C78E37}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="11_BFB1E8C370FA4DC7B436114059E362ED9305AA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60545014-21ED-4164-B067-CE86EF00F887}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
@@ -24,14 +24,15 @@
     <sheet name="Phiếu Đánh Giá Tuần 9" sheetId="9" r:id="rId9"/>
     <sheet name="Phiếu Đánh Giá Tuần 10" sheetId="11" r:id="rId10"/>
     <sheet name="Phiếu Đánh Giá Tuần 11" sheetId="12" r:id="rId11"/>
-    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId12"/>
+    <sheet name="Phiếu Đánh Giá Tuần 12" sheetId="13" r:id="rId12"/>
+    <sheet name="Cấu hình tháng" sheetId="5" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="42">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -164,6 +165,9 @@
   </si>
   <si>
     <t>Phiếu Đánh Giá Tuần 11</t>
+  </si>
+  <si>
+    <t>Phiếu Đánh Giá Tuần 12</t>
   </si>
 </sst>
 </file>
@@ -347,7 +351,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BangCauHinhThang" displayName="BangCauHinhThang" ref="A1:D13">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tên sheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tháng xếp hạng"/>
@@ -977,8 +981,156 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354F6B3-9813-4F11-A948-18B38F118EB2}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>4</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
+        <v>2</v>
+      </c>
+      <c r="I3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1181,19 +1333,33 @@
         <v>40</v>
       </c>
       <c r="B12" s="12">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="C12" s="10">
         <v>11</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="12">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="10">
+        <v>12</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D206" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="D2:D207" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Có,Không"</formula1>
     </dataValidation>
   </dataValidations>
